--- a/FEB_SUB/Data/Invalid_data_manual_review.xlsx
+++ b/FEB_SUB/Data/Invalid_data_manual_review.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8fa2471a6ec8b46c/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\surab\OneDrive\Documents\NCSU\Foodchain project\who-eats-whom\FEB_SUB\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BD1C95E-8FC9-41C9-A965-D196F2AB1B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A339EA79-7171-4A8F-9AEE-469FFA4BC3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{6E03DF35-7CAB-4171-AB94-40BA2D0AE32F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8EA239AF-DAA4-401F-9058-0A31D17A92FD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Cycles" sheetId="1" r:id="rId1"/>
+    <sheet name="Self Eating Species" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,9 +36,746 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="232">
+  <si>
+    <t>Cycles</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>My notes</t>
+  </si>
+  <si>
+    <t>Sr.no</t>
+  </si>
+  <si>
+    <t>Afrorhytida kraussi kraussi</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Alcedo atthis</t>
+  </si>
+  <si>
+    <t>Invalid enttry - The kingfisher seems to be eating a lizard here</t>
+  </si>
+  <si>
+    <t>Anolis sagrei</t>
+  </si>
+  <si>
+    <t>Apis mellifera</t>
+  </si>
+  <si>
+    <t>Araneus diadematus</t>
+  </si>
+  <si>
+    <t>Argia immunda</t>
+  </si>
+  <si>
+    <t>The argia immunda is eating some fly not sure which one</t>
+  </si>
+  <si>
+    <t>Asclepias fascicularis</t>
+  </si>
+  <si>
+    <t>Bucephala clangula</t>
+  </si>
+  <si>
+    <t>Eating a crab and not itself</t>
+  </si>
+  <si>
+    <t>Calopteryx maculata</t>
+  </si>
+  <si>
+    <t>Difficult to interpret from images</t>
+  </si>
+  <si>
+    <t>Diabrotica undecimpunctata</t>
+  </si>
+  <si>
+    <t>Dicrurus adsimilis adsimilis</t>
+  </si>
+  <si>
+    <t>Eating a bug and not itself</t>
+  </si>
+  <si>
+    <t>Erythemis simplicicollis</t>
+  </si>
+  <si>
+    <t>doesnt seem like cannibalism. The record has been changed to needs id 19days ago. Can we delete them?</t>
+  </si>
+  <si>
+    <t>Euthyrhynchus floridanus</t>
+  </si>
+  <si>
+    <t>Gerris swakopensis</t>
+  </si>
+  <si>
+    <t>Haematopus bachmani</t>
+  </si>
+  <si>
+    <t>Invalid data - A Black Oystercatcher with a greenish polychaete worm. Scavenging</t>
+  </si>
+  <si>
+    <t>Halcyon albiventris albiventris</t>
+  </si>
+  <si>
+    <t>Brown-hooded Kingfisher with a Chameleon</t>
+  </si>
+  <si>
+    <t>Harmonia axyridis</t>
+  </si>
+  <si>
+    <t>Hasarius adansoni</t>
+  </si>
+  <si>
+    <t>Jumping Spider with Ant</t>
+  </si>
+  <si>
+    <t>Hyles lineata</t>
+  </si>
+  <si>
+    <t>Jadera haematoloma</t>
+  </si>
+  <si>
+    <t>Kukulcania hibernalis</t>
+  </si>
+  <si>
+    <t>Larus fuscus</t>
+  </si>
+  <si>
+    <t>Lygodactylus capensis</t>
+  </si>
+  <si>
+    <t>Bird seems to be feeding on lizard</t>
+  </si>
+  <si>
+    <t>Lynx rufus</t>
+  </si>
+  <si>
+    <t>Misumenoides formosipes</t>
+  </si>
+  <si>
+    <t>Crab Spider with Fly</t>
+  </si>
+  <si>
+    <t>Nephilingis cruentata</t>
+  </si>
+  <si>
+    <t>African Hermit Spider eating Beetles</t>
+  </si>
+  <si>
+    <t>Oxyopes scalaris</t>
+  </si>
+  <si>
+    <t>Western Lynx Spider is feeding on Wasps</t>
+  </si>
+  <si>
+    <t>Pandion haliaetus</t>
+  </si>
+  <si>
+    <t>Panthera leo melanochaita</t>
+  </si>
+  <si>
+    <t>Pelobatrachus stejnegeri</t>
+  </si>
+  <si>
+    <t>Frog eaten by Brown-breasted Kingfisher.</t>
+  </si>
+  <si>
+    <t>Podarcis siculus</t>
+  </si>
+  <si>
+    <t>Promachus hinei</t>
+  </si>
+  <si>
+    <t>Hornet with Dragonfly</t>
+  </si>
+  <si>
+    <t>Rhus typhina</t>
+  </si>
+  <si>
+    <t>It is not eating itself</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Scathophaga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The predator is Brachycera, and the prey is Nematocera. </t>
+  </si>
+  <si>
+    <t>Sciurus carolinensis</t>
+  </si>
+  <si>
+    <t>Sylvicapra grimmia</t>
+  </si>
+  <si>
+    <t>The butt of some kind of animal, being eaten by a hyena</t>
+  </si>
+  <si>
+    <t>Sylvilagus bachmani</t>
+  </si>
+  <si>
+    <t>Parasitism</t>
+  </si>
+  <si>
+    <t>Synema globosum</t>
+  </si>
+  <si>
+    <t>A darker spider is seen on a yellow buttercup flower having captured a winged insect.</t>
+  </si>
+  <si>
+    <t>Tachycines asynamorus</t>
+  </si>
+  <si>
+    <t>Tetradactylus seps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bird eating Short-legged Seps </t>
+  </si>
+  <si>
+    <t>Toxomerus marginatus</t>
+  </si>
+  <si>
+    <t>Trema orientale</t>
+  </si>
+  <si>
+    <t>Planthoppers feeding on plants</t>
+  </si>
+  <si>
+    <t>Turdus libonyana</t>
+  </si>
+  <si>
+    <t>Bird captured a butterfly caterpillar</t>
+  </si>
+  <si>
+    <t>Uroplectes triangulifer</t>
+  </si>
+  <si>
+    <t>relationship_url</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/62278764</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/289605155</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/185235593</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/311005687</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/266155697</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/326512441</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/179761552</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/200484106</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/241314574</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/311076518</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/70876023</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/316599949</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/229978826</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/38998030</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/269731494</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/66515966</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/218843143</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/61881019</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/178284857</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/137390154</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/189363077</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/291208225</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/66517237</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/137293405</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/240907528</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/250474616</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/325830479</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/19277228</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/32936654</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/227830474</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/187342840</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/177589935</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/70937875</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/251802590</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/25191260</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/234864733</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/147248126</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/197527384</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/196790659</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/66696052</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/222344073</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/103418665</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/28488105</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/224658582</t>
+  </si>
+  <si>
+    <t>Prey scientific name</t>
+  </si>
+  <si>
+    <t>Prey common name</t>
+  </si>
+  <si>
+    <t>Prey kingdom</t>
+  </si>
+  <si>
+    <t>Predator scientific name</t>
+  </si>
+  <si>
+    <t>Predator common name</t>
+  </si>
+  <si>
+    <t>Predator kingdom</t>
+  </si>
+  <si>
+    <t>Belenois creona severina</t>
+  </si>
+  <si>
+    <t>African Common White</t>
+  </si>
+  <si>
+    <t>Animalia</t>
+  </si>
+  <si>
+    <t>Chromolaena odorata</t>
+  </si>
+  <si>
+    <t>Siam weed</t>
+  </si>
+  <si>
+    <t>Plantae</t>
+  </si>
+  <si>
+    <t>Delta fenestrale</t>
+  </si>
+  <si>
+    <t>Mylothris agathina agathina</t>
+  </si>
+  <si>
+    <t>Common Dotted Border</t>
+  </si>
+  <si>
+    <t>Telchinia serena</t>
+  </si>
+  <si>
+    <t>Dancing Amber</t>
+  </si>
+  <si>
+    <t>Lippia javanica</t>
+  </si>
+  <si>
+    <t>Fever Tea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plantae </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Animalia </t>
+  </si>
+  <si>
+    <t>Anguilla anguilla</t>
+  </si>
+  <si>
+    <t>European eel</t>
+  </si>
+  <si>
+    <t>Egretta garzetta</t>
+  </si>
+  <si>
+    <t>Little egret</t>
+  </si>
+  <si>
+    <t>Larus michahellis</t>
+  </si>
+  <si>
+    <t>Yellow-legged gull</t>
+  </si>
+  <si>
+    <t>Acanthacris ruficornis</t>
+  </si>
+  <si>
+    <t>Garden Locust</t>
+  </si>
+  <si>
+    <t>Southern Brown-hooded Kingfisher</t>
+  </si>
+  <si>
+    <t>Apiomerus californicus</t>
+  </si>
+  <si>
+    <t>California Bee Assassin</t>
+  </si>
+  <si>
+    <t>Western Honey Bee</t>
+  </si>
+  <si>
+    <t>Asclepias speciosa</t>
+  </si>
+  <si>
+    <t>showy milkweed</t>
+  </si>
+  <si>
+    <t>Papilio rutulus</t>
+  </si>
+  <si>
+    <t>Western Tiger Swallowtail</t>
+  </si>
+  <si>
+    <t>Azanus jesous</t>
+  </si>
+  <si>
+    <t>African Babul Blue</t>
+  </si>
+  <si>
+    <t>Dichrostachys cinerea</t>
+  </si>
+  <si>
+    <t>aroma</t>
+  </si>
+  <si>
+    <t>Bombus bifarius</t>
+  </si>
+  <si>
+    <t>Colorado Black-notched Bumble Bee</t>
+  </si>
+  <si>
+    <t>Solidago velutina</t>
+  </si>
+  <si>
+    <t>velvety goldenrod</t>
+  </si>
+  <si>
+    <t>Geococcyx californianus</t>
+  </si>
+  <si>
+    <t>Greater Roadrunner</t>
+  </si>
+  <si>
+    <t>Sphinx chersis</t>
+  </si>
+  <si>
+    <t>Great Ash Sphinx</t>
+  </si>
+  <si>
+    <t>Julbernardia globiflora</t>
+  </si>
+  <si>
+    <t>Mnondo</t>
+  </si>
+  <si>
+    <t>Pilostyles aethiopica</t>
+  </si>
+  <si>
+    <t>Leucophaeus atricilla</t>
+  </si>
+  <si>
+    <t>Laughing Gull</t>
+  </si>
+  <si>
+    <t>Trinectes maculatus</t>
+  </si>
+  <si>
+    <t>Hogchoker</t>
+  </si>
+  <si>
+    <t>Neoscona crucifera</t>
+  </si>
+  <si>
+    <t>Spotted Orbweaver</t>
+  </si>
+  <si>
+    <t>Greenhouse Camel Cricket</t>
+  </si>
+  <si>
+    <t>Expert Validation Required</t>
+  </si>
+  <si>
+    <t>Expert Remarks</t>
+  </si>
+  <si>
+    <t>Relationship_url</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/66415128</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/66450578</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/142450505</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/142450506</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/228896748</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/228896745</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/56967330</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/56967333</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/230630332</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/230630338</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/250649007</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/250649005</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/149463617</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/149463618</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/150509953</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/150511090</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/135098040</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/135098008</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/164485479</t>
+  </si>
+  <si>
+    <t>https://www.inaturalist.org/observations/164485487</t>
+  </si>
+  <si>
+    <t>"https://www.inaturalist.org/observations/86062718"</t>
+  </si>
+  <si>
+    <t>"https://www.inaturalist.org/observations/86062717"</t>
+  </si>
+  <si>
+    <t>"https://www.inaturalist.org/observations/86062722"</t>
+  </si>
+  <si>
+    <t>"https://www.inaturalist.org/observations/86062724"</t>
+  </si>
+  <si>
+    <t>"https://www.inaturalist.org/observations/86062723"</t>
+  </si>
+  <si>
+    <t>"https://www.inaturalist.org/observations/86169670"</t>
+  </si>
+  <si>
+    <t>"https://www.inaturalist.org/observations/86169673"</t>
+  </si>
+  <si>
+    <t>"https://www.inaturalist.org/observations/69723396"</t>
+  </si>
+  <si>
+    <t>"https://www.inaturalist.org/observations/157527462"</t>
+  </si>
+  <si>
+    <t>Seems invalid interaction</t>
+  </si>
+  <si>
+    <t>Seems like polination; not sure if its predation</t>
+  </si>
+  <si>
+    <t>Pollination; Which direction should be ideal? 2 interactions (a-&gt;b, b-&gt;a) are present</t>
+  </si>
+  <si>
+    <t>Unable to interpret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t>We identified 10  cycles. At this stage, it is unclear whether these cycles represent biologically plausible relationships. We manually reviewed them, and these interactions appear suspicious or potentially incorrect. We need a validation from an expert so that we can generate more trustworthy results</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Action Taken: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>All interactions requiring expert validation have been marked with “Yes” in the Expert Validation Required column.
+Please review these flagged interactions to confirm whether the relationships are valid so that incorrect links can be removed and the overall analysis remains accurate and trustworthy.</t>
+    </r>
+  </si>
+  <si>
+    <t>Diagram for example</t>
+  </si>
+  <si>
+    <t>Doesn’t seem like an self eating interaction</t>
+  </si>
+  <si>
+    <t>Cannibalism</t>
+  </si>
+  <si>
+    <t>Could be true; needs confirmation</t>
+  </si>
+  <si>
+    <t>Seems like Pollination</t>
+  </si>
+  <si>
+    <t>Prey seems to be termites</t>
+  </si>
+  <si>
+    <t>True (eating its larve)</t>
+  </si>
+  <si>
+    <t>Cannibalising on dead</t>
+  </si>
+  <si>
+    <t>Seems to be preying on grasshopper</t>
+  </si>
+  <si>
+    <t>Eating its on egg</t>
+  </si>
+  <si>
+    <t>Bobcat seems to be a eating a squirrel</t>
+  </si>
+  <si>
+    <t>seems to be eating a fish</t>
+  </si>
+  <si>
+    <t>Lion eating a wartdog</t>
+  </si>
+  <si>
+    <t>Self‑Eating Species</t>
+  </si>
+  <si>
+    <t>We identified 44 species that appear to be eating themselves in the dataset. Based on our review of the interaction URLs, the majority of these cases are likely incorrect or misidentified. 
+After checking the corresponding images, most still did not appear valid.
+To ensure accuracy and reliability of the interaction network, these cases must be manually validated by an expert.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Action Taken</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: All species with potential self‑eating interactions have been marked “Yes” under Expert Validation Required.
+Please review these flagged interactions and confirm whether any represent valid biological self‑predation, so that incorrect relationships can be removed and the analysis remains trustworthy.</t>
+    </r>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -45,13 +783,56 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Trebuchet MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -63,13 +844,39 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -83,6 +890,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>40666</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{338E65A2-A8B6-48DC-DBCC-7BD8C2772876}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8362950"/>
+          <a:ext cx="8934450" cy="4993666"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A11444BE-F76D-43AE-9A95-2C0708311DD0}" name="Table1" displayName="Table1" ref="A5:J37" totalsRowShown="0">
+  <autoFilter ref="A5:J37" xr:uid="{A11444BE-F76D-43AE-9A95-2C0708311DD0}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{2364DA3D-7612-43B1-89CC-0269F22185C3}" name="Prey scientific name"/>
+    <tableColumn id="2" xr3:uid="{2128B86A-F24A-4085-A603-4EB4EF365AA6}" name="Prey common name"/>
+    <tableColumn id="3" xr3:uid="{1CB1A5FA-7074-4453-9727-79D5BDB84FF9}" name="Prey kingdom"/>
+    <tableColumn id="4" xr3:uid="{E0831D00-1EE9-4E48-8EEE-555B9D496B28}" name="Predator scientific name"/>
+    <tableColumn id="5" xr3:uid="{70FD7468-4FA3-4D6A-9D51-C065130176A5}" name="Predator common name"/>
+    <tableColumn id="6" xr3:uid="{F707FCAA-26B3-46A7-8DFD-72E4E393D64D}" name="Predator kingdom"/>
+    <tableColumn id="7" xr3:uid="{DC4DA42A-2867-42C5-A06D-38F4023D84D2}" name="Relationship_url" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{2A226FB4-EE39-4728-92FB-52E875C42D72}" name="My notes"/>
+    <tableColumn id="9" xr3:uid="{0B8A2A13-0FB7-4371-B92A-AB3D151DBD07}" name="Expert Validation Required"/>
+    <tableColumn id="10" xr3:uid="{7DB63A32-81D3-4CF2-AE37-4675FF0AC633}" name="Expert Remarks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7ED3401B-9F59-4B64-AC5D-588AEC658560}" name="Table2" displayName="Table2" ref="A6:F50" totalsRowShown="0">
+  <autoFilter ref="A6:F50" xr:uid="{7ED3401B-9F59-4B64-AC5D-588AEC658560}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{F5BF1C0C-9E2F-42E1-ABC8-39D5360B3BF4}" name="Sr.no"/>
+    <tableColumn id="2" xr3:uid="{0310A695-24C9-4526-9CBC-A37E7DF5A6D4}" name="Name"/>
+    <tableColumn id="3" xr3:uid="{F6AE690C-B802-49D6-80A8-280A6E85A3CA}" name="relationship_url"/>
+    <tableColumn id="4" xr3:uid="{1EC21599-3027-42BE-A22A-B7DA4D16C693}" name="My notes"/>
+    <tableColumn id="5" xr3:uid="{EB75DCCB-6CAF-47A7-A0B8-2352677C7725}" name="Expert Validation Required"/>
+    <tableColumn id="6" xr3:uid="{60EC9856-CCD1-4FDB-B3F1-1610C5A66202}" name="Expert Remarks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -401,10 +1291,1907 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CA50989-174B-43B3-9E74-2C303027D8D9}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{377968A4-C4C0-4F19-AE4A-B37D3185CC65}">
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="50.85546875" customWidth="1"/>
+    <col min="8" max="8" width="28.85546875" customWidth="1"/>
+    <col min="9" max="9" width="29.28515625" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G5" t="s">
+        <v>179</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H6" t="s">
+        <v>210</v>
+      </c>
+      <c r="I6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H7" t="s">
+        <v>209</v>
+      </c>
+      <c r="I7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H8" t="s">
+        <v>209</v>
+      </c>
+      <c r="I8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H9" t="s">
+        <v>209</v>
+      </c>
+      <c r="I9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H10" t="s">
+        <v>209</v>
+      </c>
+      <c r="I10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H11" t="s">
+        <v>210</v>
+      </c>
+      <c r="I11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H13" t="s">
+        <v>210</v>
+      </c>
+      <c r="I13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" t="s">
+        <v>210</v>
+      </c>
+      <c r="I14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H15" t="s">
+        <v>210</v>
+      </c>
+      <c r="I15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" t="s">
+        <v>142</v>
+      </c>
+      <c r="F16" t="s">
+        <v>126</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E17" t="s">
+        <v>144</v>
+      </c>
+      <c r="F17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H18" t="s">
+        <v>209</v>
+      </c>
+      <c r="I18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H19" t="s">
+        <v>209</v>
+      </c>
+      <c r="I19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" t="s">
+        <v>126</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" t="s">
+        <v>146</v>
+      </c>
+      <c r="F21" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H21" t="s">
+        <v>209</v>
+      </c>
+      <c r="I21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H22" t="s">
+        <v>209</v>
+      </c>
+      <c r="I22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E23" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B24" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24" t="s">
+        <v>126</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H24" t="s">
+        <v>211</v>
+      </c>
+      <c r="I24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" t="s">
+        <v>129</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H25" t="s">
+        <v>211</v>
+      </c>
+      <c r="I25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F26" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H26" t="s">
+        <v>209</v>
+      </c>
+      <c r="I26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" t="s">
+        <v>155</v>
+      </c>
+      <c r="E27" t="s">
+        <v>156</v>
+      </c>
+      <c r="F27" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H28" t="s">
+        <v>211</v>
+      </c>
+      <c r="I28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H29" t="s">
+        <v>211</v>
+      </c>
+      <c r="I29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" t="s">
+        <v>165</v>
+      </c>
+      <c r="E30" t="s">
+        <v>166</v>
+      </c>
+      <c r="F30" t="s">
+        <v>126</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H30" t="s">
+        <v>209</v>
+      </c>
+      <c r="I30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" t="s">
+        <v>163</v>
+      </c>
+      <c r="E31" t="s">
+        <v>164</v>
+      </c>
+      <c r="F31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>167</v>
+      </c>
+      <c r="B32" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" t="s">
+        <v>169</v>
+      </c>
+      <c r="F32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H32" t="s">
+        <v>209</v>
+      </c>
+      <c r="I32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>169</v>
+      </c>
+      <c r="C33" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" t="s">
+        <v>168</v>
+      </c>
+      <c r="F33" t="s">
+        <v>129</v>
+      </c>
+      <c r="G33" t="s">
+        <v>193</v>
+      </c>
+      <c r="H33" t="s">
+        <v>209</v>
+      </c>
+      <c r="I33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" t="s">
+        <v>126</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H34" t="s">
+        <v>209</v>
+      </c>
+      <c r="I34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C35" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" t="s">
+        <v>170</v>
+      </c>
+      <c r="E35" t="s">
+        <v>171</v>
+      </c>
+      <c r="F35" t="s">
+        <v>126</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36" t="s">
+        <v>175</v>
+      </c>
+      <c r="C36" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" t="s">
+        <v>176</v>
+      </c>
+      <c r="F36" t="s">
+        <v>126</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" t="s">
+        <v>212</v>
+      </c>
+      <c r="I36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" t="s">
+        <v>176</v>
+      </c>
+      <c r="C37" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" t="s">
+        <v>174</v>
+      </c>
+      <c r="E37" t="s">
+        <v>175</v>
+      </c>
+      <c r="F37" t="s">
+        <v>126</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H37" t="s">
+        <v>212</v>
+      </c>
+      <c r="I37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:F15">
+    <sortCondition ref="A6:A15"/>
+  </sortState>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{FB2E6F99-316A-4C2E-9694-1F4B0B27860B}"/>
+    <hyperlink ref="G12" r:id="rId2" xr:uid="{27B2A646-B5A4-4498-AD44-B187445F412E}"/>
+    <hyperlink ref="G9" r:id="rId3" display="https://www.inaturalist.org/observations/86062718" xr:uid="{8852E3C0-253E-4501-AB32-A805255239C8}"/>
+    <hyperlink ref="G14" r:id="rId4" display="https://www.inaturalist.org/observations/86062717" xr:uid="{AC4A8E78-0D87-4E78-ADD6-209EA82769CC}"/>
+    <hyperlink ref="G8" r:id="rId5" display="https://www.inaturalist.org/observations/86062722" xr:uid="{EAEE1A15-0EFC-4BF5-9E98-0FB68A61722D}"/>
+    <hyperlink ref="G11" r:id="rId6" display="https://www.inaturalist.org/observations/86062717" xr:uid="{61139763-37E6-476E-BB3D-56FE4A493C77}"/>
+    <hyperlink ref="G7" r:id="rId7" display="https://www.inaturalist.org/observations/86062724" xr:uid="{3BD6DC82-1EBF-41A7-B051-4803ED0CC1C4}"/>
+    <hyperlink ref="G6" r:id="rId8" display="https://www.inaturalist.org/observations/86062717" xr:uid="{3F4BCB0A-A3C5-4099-9BCC-A8333F518638}"/>
+    <hyperlink ref="G10" r:id="rId9" display="https://www.inaturalist.org/observations/86062723" xr:uid="{FF4980E2-6E62-41BE-9C2E-CF814A84BED7}"/>
+    <hyperlink ref="G15" r:id="rId10" display="https://www.inaturalist.org/observations/86062717" xr:uid="{8E645DB6-4FF8-4D9B-8BE5-82CB6B1526A1}"/>
+    <hyperlink ref="G16" r:id="rId11" display="https://www.inaturalist.org/observations/86169670" xr:uid="{EEEBB1D7-91D0-43E8-BC1F-E6DDF1B98A50}"/>
+    <hyperlink ref="G18" r:id="rId12" display="https://www.inaturalist.org/observations/86169673" xr:uid="{F552D45A-FF9A-4B3F-A63D-5026DE9B2F5D}"/>
+    <hyperlink ref="G19" r:id="rId13" display="https://www.inaturalist.org/observations/69723396" xr:uid="{61276E4D-B07C-4EAE-BCC6-513E872595D7}"/>
+    <hyperlink ref="G17" r:id="rId14" display="https://www.inaturalist.org/observations/157527462" xr:uid="{B3C5BCAD-B023-4BAE-8660-CF6E29B8BE1B}"/>
+    <hyperlink ref="G20" r:id="rId15" xr:uid="{D2547EE1-5354-486E-862F-DC096089700F}"/>
+    <hyperlink ref="G21" r:id="rId16" xr:uid="{61CDC823-77AA-4F54-A717-C2E2223E2615}"/>
+    <hyperlink ref="G22" r:id="rId17" xr:uid="{F5D1C947-1BC2-48D3-B66D-24E45019BDBC}"/>
+    <hyperlink ref="G23" r:id="rId18" xr:uid="{1B9A1970-6F65-423B-9E13-2A91460D6573}"/>
+    <hyperlink ref="G24" r:id="rId19" xr:uid="{813737FA-C01E-403F-A5A4-EC9E6DBF6E46}"/>
+    <hyperlink ref="G25" r:id="rId20" xr:uid="{4C1D2506-247D-49C5-B6ED-2BBA1D19AF87}"/>
+    <hyperlink ref="G26" r:id="rId21" xr:uid="{3536E044-F472-45C9-AEED-72C222FE23AF}"/>
+    <hyperlink ref="G27" r:id="rId22" xr:uid="{A4803CEE-A017-4FDE-A4F8-56E2CB1CE957}"/>
+    <hyperlink ref="G28" r:id="rId23" xr:uid="{BE072F4E-7AA8-4501-9CEA-CA5CA16A3CC9}"/>
+    <hyperlink ref="G29" r:id="rId24" xr:uid="{205FB4E8-9520-424D-B618-D00166A8F1E9}"/>
+    <hyperlink ref="G30" r:id="rId25" xr:uid="{59610AC8-4171-41E0-9C80-36FBB46FE4DD}"/>
+    <hyperlink ref="G31" r:id="rId26" xr:uid="{B24D6EAE-9385-495A-A507-A4F71B3B5BEE}"/>
+    <hyperlink ref="G32" r:id="rId27" xr:uid="{336737DC-BEF7-47C2-894C-3DED6782F946}"/>
+    <hyperlink ref="G34" r:id="rId28" xr:uid="{205C3C43-32C6-4EFF-8D63-00F4F6FBECA8}"/>
+    <hyperlink ref="G35" r:id="rId29" xr:uid="{9BEDFE61-15BF-4AA9-9ADF-3923ED57ABA1}"/>
+    <hyperlink ref="G36" r:id="rId30" xr:uid="{F0F64D48-CF23-4BB4-A9E8-E39A8C3C6C16}"/>
+    <hyperlink ref="G37" r:id="rId31" xr:uid="{B05F19D4-073C-411A-A6F5-D11836A09B05}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId32"/>
+  <tableParts count="1">
+    <tablePart r:id="rId33"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{634C9953-0FF2-4585-BD0F-4445F06620C5}">
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.140625" customWidth="1"/>
+    <col min="4" max="4" width="46.28515625" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+    </row>
+    <row r="2" spans="1:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>220</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" t="s">
+        <v>221</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" t="s">
+        <v>222</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" t="s">
+        <v>223</v>
+      </c>
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" t="s">
+        <v>224</v>
+      </c>
+      <c r="E27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" t="s">
+        <v>225</v>
+      </c>
+      <c r="E28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" t="s">
+        <v>226</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>26</v>
+      </c>
+      <c r="B32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>27</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" t="s">
+        <v>227</v>
+      </c>
+      <c r="E34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>29</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>30</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>31</v>
+      </c>
+      <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>34</v>
+      </c>
+      <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>35</v>
+      </c>
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>36</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>38</v>
+      </c>
+      <c r="B44" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" t="s">
+        <v>111</v>
+      </c>
+      <c r="D44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>39</v>
+      </c>
+      <c r="B45" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E45" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>40</v>
+      </c>
+      <c r="B46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" t="s">
+        <v>66</v>
+      </c>
+      <c r="E46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>41</v>
+      </c>
+      <c r="B47" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" t="s">
+        <v>220</v>
+      </c>
+      <c r="E47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>42</v>
+      </c>
+      <c r="B48" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" t="s">
+        <v>115</v>
+      </c>
+      <c r="D48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>43</v>
+      </c>
+      <c r="B49" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" t="s">
+        <v>116</v>
+      </c>
+      <c r="D49" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>44</v>
+      </c>
+      <c r="B50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" t="s">
+        <v>117</v>
+      </c>
+      <c r="D50" t="s">
+        <v>219</v>
+      </c>
+      <c r="E50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C7" r:id="rId1" xr:uid="{2D298A5B-12DE-4383-84C4-913DD88332ED}"/>
+    <hyperlink ref="C8" r:id="rId2" xr:uid="{AC2C6004-41C2-465F-9FDD-83F39D83A302}"/>
+    <hyperlink ref="C9" r:id="rId3" xr:uid="{CA72D88E-DF8E-47AE-9C26-967E7C80D919}"/>
+    <hyperlink ref="C10" r:id="rId4" xr:uid="{47BDECE0-9DAD-4CD1-9D52-881935C114C3}"/>
+    <hyperlink ref="C11" r:id="rId5" xr:uid="{C8D9B083-4B4A-4807-844F-4C8C59614E2B}"/>
+    <hyperlink ref="C19" r:id="rId6" xr:uid="{E4B9DB40-3261-4DC9-92CC-136F5B512BCB}"/>
+    <hyperlink ref="C20" r:id="rId7" xr:uid="{0E899030-147D-492A-A780-FFAF7F852A15}"/>
+    <hyperlink ref="C23" r:id="rId8" xr:uid="{0BE4DCE5-44D3-4B73-9E8A-9C957C401B5A}"/>
+    <hyperlink ref="C25" r:id="rId9" xr:uid="{8BCB6393-6483-4E77-902F-3BF04076554A}"/>
+    <hyperlink ref="C26" r:id="rId10" xr:uid="{92143D28-D9FE-48AB-9B3C-AE53756045D6}"/>
+    <hyperlink ref="C27" r:id="rId11" xr:uid="{B529D8CC-CD9E-4B5D-8052-FE00AA5C2032}"/>
+    <hyperlink ref="C28" r:id="rId12" xr:uid="{D313621D-73A8-4455-A03E-7EBD018815D9}"/>
+    <hyperlink ref="C30" r:id="rId13" xr:uid="{CC52BE3C-0D15-4FF5-8308-28A4BAD370F2}"/>
+    <hyperlink ref="C34" r:id="rId14" xr:uid="{95A9E8AF-BBD9-4009-9625-FE575A792132}"/>
+    <hyperlink ref="C35" r:id="rId15" xr:uid="{0892007D-B762-4785-9E3A-9427FDA20D75}"/>
+    <hyperlink ref="C37" r:id="rId16" xr:uid="{8A66F4B0-A221-4BF7-A320-D28AF2097672}"/>
+    <hyperlink ref="C45" r:id="rId17" xr:uid="{97139905-5037-455A-9D41-8AB50B9447F4}"/>
+    <hyperlink ref="C47" r:id="rId18" xr:uid="{39D6FF69-803C-467D-A07C-CF78260359E4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId19"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/FEB_SUB/Data/Invalid_data_manual_review.xlsx
+++ b/FEB_SUB/Data/Invalid_data_manual_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\surab\OneDrive\Documents\NCSU\Foodchain project\who-eats-whom\FEB_SUB\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A339EA79-7171-4A8F-9AEE-469FFA4BC3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EE4888-0495-47E0-9F43-2ECCACDEF4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8EA239AF-DAA4-401F-9058-0A31D17A92FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8EA239AF-DAA4-401F-9058-0A31D17A92FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Cycles" sheetId="1" r:id="rId1"/>
@@ -684,8 +684,79 @@
     <t>We identified 10  cycles. At this stage, it is unclear whether these cycles represent biologically plausible relationships. We manually reviewed them, and these interactions appear suspicious or potentially incorrect. We need a validation from an expert so that we can generate more trustworthy results</t>
   </si>
   <si>
+    <t>Diagram for example</t>
+  </si>
+  <si>
+    <t>Doesn’t seem like an self eating interaction</t>
+  </si>
+  <si>
+    <t>Cannibalism</t>
+  </si>
+  <si>
+    <t>Could be true; needs confirmation</t>
+  </si>
+  <si>
+    <t>Seems like Pollination</t>
+  </si>
+  <si>
+    <t>Prey seems to be termites</t>
+  </si>
+  <si>
+    <t>True (eating its larve)</t>
+  </si>
+  <si>
+    <t>Cannibalising on dead</t>
+  </si>
+  <si>
+    <t>Seems to be preying on grasshopper</t>
+  </si>
+  <si>
+    <t>Eating its on egg</t>
+  </si>
+  <si>
+    <t>Bobcat seems to be a eating a squirrel</t>
+  </si>
+  <si>
+    <t>seems to be eating a fish</t>
+  </si>
+  <si>
+    <t>Lion eating a wartdog</t>
+  </si>
+  <si>
+    <t>Self‑Eating Species</t>
+  </si>
+  <si>
+    <t>We identified 44 species that appear to be eating themselves in the dataset. Based on our review of the interaction URLs, the majority of these cases are likely incorrect or misidentified. 
+After checking the corresponding images, most still did not appear valid.
+To ensure accuracy and reliability of the interaction network, these cases must be manually validated by an expert.</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Action Taken: </t>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Action Needed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: All species with potential self‑eating interactions have been marked “Yes” under Expert Validation Required.
+Please review these flagged interactions and confirm whether any represent valid biological self‑predation, so that incorrect relationships can be removed and the analysis remains trustworthy.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Action Needed: </t>
     </r>
     <r>
       <rPr>
@@ -697,77 +768,6 @@
       </rPr>
       <t>All interactions requiring expert validation have been marked with “Yes” in the Expert Validation Required column.
 Please review these flagged interactions to confirm whether the relationships are valid so that incorrect links can be removed and the overall analysis remains accurate and trustworthy.</t>
-    </r>
-  </si>
-  <si>
-    <t>Diagram for example</t>
-  </si>
-  <si>
-    <t>Doesn’t seem like an self eating interaction</t>
-  </si>
-  <si>
-    <t>Cannibalism</t>
-  </si>
-  <si>
-    <t>Could be true; needs confirmation</t>
-  </si>
-  <si>
-    <t>Seems like Pollination</t>
-  </si>
-  <si>
-    <t>Prey seems to be termites</t>
-  </si>
-  <si>
-    <t>True (eating its larve)</t>
-  </si>
-  <si>
-    <t>Cannibalising on dead</t>
-  </si>
-  <si>
-    <t>Seems to be preying on grasshopper</t>
-  </si>
-  <si>
-    <t>Eating its on egg</t>
-  </si>
-  <si>
-    <t>Bobcat seems to be a eating a squirrel</t>
-  </si>
-  <si>
-    <t>seems to be eating a fish</t>
-  </si>
-  <si>
-    <t>Lion eating a wartdog</t>
-  </si>
-  <si>
-    <t>Self‑Eating Species</t>
-  </si>
-  <si>
-    <t>We identified 44 species that appear to be eating themselves in the dataset. Based on our review of the interaction URLs, the majority of these cases are likely incorrect or misidentified. 
-After checking the corresponding images, most still did not appear valid.
-To ensure accuracy and reliability of the interaction network, these cases must be manually validated by an expert.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Action Taken</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: All species with potential self‑eating interactions have been marked “Yes” under Expert Validation Required.
-Please review these flagged interactions and confirm whether any represent valid biological self‑predation, so that incorrect relationships can be removed and the analysis remains trustworthy.</t>
     </r>
   </si>
 </sst>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="3" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2299,7 +2299,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2367,7 +2367,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2377,7 +2377,7 @@
     </row>
     <row r="2" spans="1:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -2426,7 +2426,7 @@
         <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -2460,7 +2460,7 @@
         <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E9" t="s">
         <v>54</v>
@@ -2477,7 +2477,7 @@
         <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -2528,7 +2528,7 @@
         <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -2579,7 +2579,7 @@
         <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -2630,7 +2630,7 @@
         <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -2647,7 +2647,7 @@
         <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
@@ -2698,7 +2698,7 @@
         <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E23" t="s">
         <v>54</v>
@@ -2732,7 +2732,7 @@
         <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -2749,7 +2749,7 @@
         <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E26" t="s">
         <v>54</v>
@@ -2766,7 +2766,7 @@
         <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
@@ -2783,7 +2783,7 @@
         <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E28" t="s">
         <v>54</v>
@@ -2817,7 +2817,7 @@
         <v>97</v>
       </c>
       <c r="D30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
@@ -2885,7 +2885,7 @@
         <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
@@ -2902,7 +2902,7 @@
         <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E35" t="s">
         <v>5</v>
@@ -2936,7 +2936,7 @@
         <v>104</v>
       </c>
       <c r="D37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E37" t="s">
         <v>54</v>
@@ -3072,7 +3072,7 @@
         <v>112</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E45" t="s">
         <v>54</v>
@@ -3106,7 +3106,7 @@
         <v>114</v>
       </c>
       <c r="D47" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E47" t="s">
         <v>5</v>
@@ -3157,7 +3157,7 @@
         <v>117</v>
       </c>
       <c r="D50" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E50" t="s">
         <v>5</v>

--- a/FEB_SUB/Data/Invalid_data_manual_review.xlsx
+++ b/FEB_SUB/Data/Invalid_data_manual_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\surab\OneDrive\Documents\NCSU\Foodchain project\who-eats-whom\FEB_SUB\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0014A9E-040F-4689-85F2-1AFCC9BF0D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19653AE5-E78B-4D2C-8F1B-2128BEC76E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8EA239AF-DAA4-401F-9058-0A31D17A92FD}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{8EA239AF-DAA4-401F-9058-0A31D17A92FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Cycles" sheetId="1" r:id="rId1"/>
@@ -851,7 +851,12 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -860,19 +865,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1308,46 +1308,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -2298,7 +2298,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="2" t="s">
         <v>215</v>
       </c>
     </row>
@@ -2366,34 +2366,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
     </row>
     <row r="3" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -3071,7 +3071,7 @@
       <c r="C45" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="3" t="s">
         <v>217</v>
       </c>
       <c r="E45" t="s">
